--- a/eval-suite/cases/006_dwb_user_behavior_f/mapping.xlsx
+++ b/eval-suite/cases/006_dwb_user_behavior_f/mapping.xlsx
@@ -1195,10 +1195,9 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>dwb_user_behavior_f</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>dwb_user_behavior_i</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>主表</t>
@@ -1209,7 +1208,6 @@
           <t>场景1-电商交易</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1252,10 +1250,9 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>dwb_user_behavior_f</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>dwb_user_behavior_i</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>LEFT JOIN ON o.product_id = p.product_id</t>
@@ -1266,7 +1263,6 @@
           <t>场景1-商品信息</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4" ht="31" customHeight="1">
       <c r="A4" t="n">
@@ -1309,10 +1305,9 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>dwb_user_behavior_f</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>dwb_user_behavior_i</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>LEFT JOIN ON o.user_id = u.user_id</t>
@@ -1323,7 +1318,6 @@
           <t>场景1-用户信息</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1366,10 +1360,9 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>dwb_user_behavior_f</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>dwb_user_behavior_i</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>主表</t>
@@ -1380,7 +1373,6 @@
           <t>场景2-内容互动</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1423,10 +1415,9 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>dwb_user_behavior_f</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>dwb_user_behavior_i</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>LEFT JOIN ON c.content_id = ct.content_id</t>
@@ -1437,7 +1428,6 @@
           <t>场景2-内容信息</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1480,10 +1470,9 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>dwb_user_behavior_f</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>dwb_user_behavior_i</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>LEFT JOIN ON c.user_id = u.user_id</t>
@@ -1494,7 +1483,6 @@
           <t>场景2-用户信息</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1537,10 +1525,9 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>dwb_user_behavior_f</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>dwb_user_behavior_i</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>主表</t>
@@ -1551,7 +1538,6 @@
           <t>场景3-社交关系</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1594,10 +1580,9 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>dwb_user_behavior_f</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>dwb_user_behavior_i</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>LEFT JOIN ON s.user_id = up.user_id</t>
@@ -1608,7 +1593,6 @@
           <t>场景3-用户画像</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1651,10 +1635,9 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>dwb_user_behavior_f</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>dwb_user_behavior_i</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>LEFT JOIN ON s.user_id = u.user_id</t>
@@ -1665,7 +1648,6 @@
           <t>场景3-用户信息</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1836,7 +1818,6 @@
           <t>主键</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3" ht="31" customHeight="1">
       <c r="A3" t="n">
@@ -1902,8 +1883,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" t="n">
@@ -1969,8 +1948,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5" ht="76" customHeight="1">
       <c r="A5" t="n">
@@ -2036,8 +2013,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6" ht="122" customHeight="1">
       <c r="A6" t="n">
@@ -2103,8 +2078,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7" ht="122" customHeight="1">
       <c r="A7" t="n">
@@ -2170,8 +2143,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8" ht="122" customHeight="1">
       <c r="A8" t="n">
@@ -2237,8 +2208,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9" ht="122" customHeight="1">
       <c r="A9" t="n">
@@ -2304,8 +2273,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" t="n">
@@ -2371,8 +2338,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11" ht="137" customHeight="1">
       <c r="A11" t="n">
@@ -2438,8 +2403,6 @@
           <t>varchar(10)</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12" ht="152" customHeight="1">
       <c r="A12" t="n">
@@ -2505,8 +2468,6 @@
           <t>varchar(10)</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13" ht="76" customHeight="1">
       <c r="A13" t="n">
@@ -2572,8 +2533,6 @@
           <t>varchar(10)</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2639,8 +2598,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2706,8 +2663,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2773,8 +2728,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2840,8 +2793,6 @@
           <t>date</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2907,8 +2858,6 @@
           <t>date</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2974,8 +2923,6 @@
           <t>date</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3041,8 +2988,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3108,8 +3053,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3175,8 +3118,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3242,8 +3183,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3309,8 +3248,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3376,8 +3313,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3443,8 +3378,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3510,8 +3443,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3577,8 +3508,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3644,8 +3573,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3711,8 +3638,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3778,8 +3703,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3845,8 +3768,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3912,8 +3833,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3979,8 +3898,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4046,8 +3963,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4113,8 +4028,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4180,8 +4093,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4247,8 +4158,6 @@
           <t>date</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4314,8 +4223,6 @@
           <t>date</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4381,8 +4288,6 @@
           <t>date</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4448,8 +4353,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4515,8 +4418,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4582,8 +4483,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4649,8 +4548,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4716,8 +4613,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4783,8 +4678,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4850,8 +4743,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4917,8 +4808,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4984,8 +4873,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5051,8 +4938,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5118,8 +5003,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5185,8 +5068,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5252,8 +5133,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5319,8 +5198,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5386,8 +5263,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5453,8 +5328,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5520,8 +5393,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5587,8 +5458,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5654,8 +5523,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5721,8 +5588,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5788,8 +5653,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5855,8 +5718,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5922,8 +5783,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5989,8 +5848,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6056,8 +5913,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6123,8 +5978,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -6190,8 +6043,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -6257,8 +6108,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6324,8 +6173,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6391,8 +6238,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6458,8 +6303,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6525,8 +6368,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6592,8 +6433,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6659,8 +6498,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6726,8 +6563,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6793,8 +6628,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6860,8 +6693,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6927,8 +6758,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6994,8 +6823,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -7061,8 +6888,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -7128,8 +6953,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -7195,8 +7018,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -7262,8 +7083,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -7329,8 +7148,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -7396,8 +7213,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -7463,8 +7278,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -7530,8 +7343,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -7597,8 +7408,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -7664,8 +7473,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -7731,8 +7538,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -7798,8 +7603,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -7865,8 +7668,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -7932,8 +7733,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -7999,8 +7798,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -8066,8 +7863,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -8133,8 +7928,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -8200,8 +7993,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -8267,8 +8058,6 @@
           <t>date</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -8334,8 +8123,6 @@
           <t>date</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -8401,8 +8188,6 @@
           <t>date</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -8468,8 +8253,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -8535,8 +8318,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -8602,8 +8383,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -8669,8 +8448,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -8736,8 +8513,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -8803,8 +8578,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -8870,8 +8643,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -8937,8 +8708,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -9004,8 +8773,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -9071,8 +8838,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -9138,8 +8903,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -9205,8 +8968,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -9272,8 +9033,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -9339,8 +9098,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -9406,8 +9163,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -9473,8 +9228,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -9540,8 +9293,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -9607,8 +9358,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -9674,8 +9423,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -9741,8 +9488,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -9808,8 +9553,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -9875,8 +9618,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -9942,8 +9683,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -10009,8 +9748,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -10076,8 +9813,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -10143,8 +9878,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -10210,8 +9943,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -10277,8 +10008,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -10344,8 +10073,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -10411,8 +10138,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -10478,8 +10203,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -10545,8 +10268,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -10612,8 +10333,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -10679,8 +10398,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -10746,8 +10463,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -10813,8 +10528,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -10880,8 +10593,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -10947,8 +10658,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -11014,8 +10723,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -11081,8 +10788,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -11148,8 +10853,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -11215,8 +10918,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -11282,8 +10983,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -11349,8 +11048,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -11416,8 +11113,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -11483,8 +11178,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -11550,8 +11243,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -11617,8 +11308,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -11684,8 +11373,6 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -11751,8 +11438,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -11818,8 +11503,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -11885,8 +11568,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -11952,8 +11633,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -12019,8 +11698,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -12086,8 +11763,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -12153,8 +11828,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -12220,8 +11893,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -12287,8 +11958,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -12354,8 +12023,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -12421,8 +12088,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -12488,8 +12153,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -12555,8 +12218,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -12622,8 +12283,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -12689,8 +12348,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -12756,8 +12413,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr"/>
-      <c r="O165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -12823,8 +12478,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -12890,8 +12543,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -12957,8 +12608,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -13024,8 +12673,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -13091,8 +12738,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -13158,8 +12803,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -13225,8 +12868,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -13292,8 +12933,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -13359,8 +12998,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -13426,8 +13063,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -13493,8 +13128,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -13560,8 +13193,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -13627,8 +13258,6 @@
           <t>varchar(1000)</t>
         </is>
       </c>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -13694,8 +13323,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -13761,8 +13388,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -13828,8 +13453,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -13895,8 +13518,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -13962,8 +13583,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -14029,8 +13648,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -14096,8 +13713,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -14163,8 +13778,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -14230,8 +13843,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -14297,8 +13908,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -14364,8 +13973,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -14431,8 +14038,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -14498,8 +14103,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -14565,8 +14168,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -14632,8 +14233,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -14699,8 +14298,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -14766,8 +14363,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -14833,8 +14428,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -14900,8 +14493,6 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -14967,8 +14558,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -15034,8 +14623,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -15101,8 +14688,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -15168,8 +14753,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -15235,8 +14818,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -15302,8 +14883,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -15369,8 +14948,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -15436,8 +15013,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -15503,8 +15078,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -15570,8 +15143,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -15637,8 +15208,6 @@
           <t>date</t>
         </is>
       </c>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -15704,8 +15273,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -15771,8 +15338,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -15838,8 +15403,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N211" t="inlineStr"/>
-      <c r="O211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -15905,8 +15468,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -15972,8 +15533,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr"/>
-      <c r="O213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -16039,8 +15598,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -16106,8 +15663,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -16173,8 +15728,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -16240,8 +15793,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -16307,8 +15858,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -16374,8 +15923,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -16441,8 +15988,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -16508,8 +16053,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -16575,8 +16118,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -16642,8 +16183,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N223" t="inlineStr"/>
-      <c r="O223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -16709,8 +16248,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N224" t="inlineStr"/>
-      <c r="O224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -16776,8 +16313,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -16843,8 +16378,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -16910,8 +16443,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -16977,8 +16508,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr"/>
-      <c r="O228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -17044,8 +16573,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N229" t="inlineStr"/>
-      <c r="O229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -17111,8 +16638,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N230" t="inlineStr"/>
-      <c r="O230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -17178,8 +16703,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -17245,8 +16768,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -17312,8 +16833,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N233" t="inlineStr"/>
-      <c r="O233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -17379,8 +16898,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N234" t="inlineStr"/>
-      <c r="O234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -17446,8 +16963,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr"/>
-      <c r="O235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -17513,8 +17028,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N236" t="inlineStr"/>
-      <c r="O236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -17580,8 +17093,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N237" t="inlineStr"/>
-      <c r="O237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -17647,8 +17158,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -17714,8 +17223,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N239" t="inlineStr"/>
-      <c r="O239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -17781,8 +17288,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N240" t="inlineStr"/>
-      <c r="O240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -17848,8 +17353,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N241" t="inlineStr"/>
-      <c r="O241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -17915,8 +17418,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N242" t="inlineStr"/>
-      <c r="O242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -17982,8 +17483,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N243" t="inlineStr"/>
-      <c r="O243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -18049,8 +17548,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N244" t="inlineStr"/>
-      <c r="O244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -18116,8 +17613,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N245" t="inlineStr"/>
-      <c r="O245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -18183,8 +17678,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N246" t="inlineStr"/>
-      <c r="O246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -18250,8 +17743,6 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="N247" t="inlineStr"/>
-      <c r="O247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -18317,8 +17808,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N248" t="inlineStr"/>
-      <c r="O248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -18384,8 +17873,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N249" t="inlineStr"/>
-      <c r="O249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -18451,8 +17938,6 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="N250" t="inlineStr"/>
-      <c r="O250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -18518,8 +18003,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N251" t="inlineStr"/>
-      <c r="O251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -18585,8 +18068,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N252" t="inlineStr"/>
-      <c r="O252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -18652,8 +18133,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N253" t="inlineStr"/>
-      <c r="O253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -18719,8 +18198,6 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="N254" t="inlineStr"/>
-      <c r="O254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -18786,8 +18263,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N255" t="inlineStr"/>
-      <c r="O255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -18853,8 +18328,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N256" t="inlineStr"/>
-      <c r="O256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -18920,8 +18393,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N257" t="inlineStr"/>
-      <c r="O257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -18987,8 +18458,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N258" t="inlineStr"/>
-      <c r="O258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -19054,8 +18523,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N259" t="inlineStr"/>
-      <c r="O259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -19121,8 +18588,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N260" t="inlineStr"/>
-      <c r="O260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -19188,8 +18653,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N261" t="inlineStr"/>
-      <c r="O261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -19200,12 +18663,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr"/>
-      <c r="D262" t="inlineStr"/>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
-      <c r="G262" t="inlineStr"/>
-      <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -19236,7 +18693,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -19247,12 +18703,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr"/>
-      <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
-      <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -19283,7 +18733,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -19294,12 +18743,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr"/>
-      <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr"/>
-      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -19330,7 +18773,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -19341,12 +18783,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr"/>
-      <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -19377,7 +18813,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O265" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/eval-suite/cases/006_dwb_user_behavior_f/mapping.xlsx
+++ b/eval-suite/cases/006_dwb_user_behavior_f/mapping.xlsx
@@ -1695,7 +1695,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>源表物理表别名</t>
+          <t>源表别名</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
